--- a/AI Audit Log_DE190499.xlsx
+++ b/AI Audit Log_DE190499.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FPT Uni\Major5\SWP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FPT Uni\Major5\SWP\ai-audit-log-btuejan11\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE15049F-D181-4531-9563-A5A333F956CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBA6AA1D-0B1A-4875-A1A8-7F48C0290D05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>STT (Entry #)</t>
   </si>
@@ -47,6 +47,9 @@
   <si>
     <t>Human Delta &amp; Reflection 
 (Phần quan trọng nhất)</t>
+  </si>
+  <si>
+    <t>ưqqdq</t>
   </si>
 </sst>
 </file>
@@ -370,14 +373,16 @@
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="1"/>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="C2" s="1"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>

--- a/AI Audit Log_DE190499.xlsx
+++ b/AI Audit Log_DE190499.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FPT Uni\Major5\SWP\ai-audit-log-btuejan11\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBA6AA1D-0B1A-4875-A1A8-7F48C0290D05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B338C2CB-67F3-4725-92F1-107F457D19AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>STT (Entry #)</t>
   </si>
@@ -49,14 +49,29 @@
 (Phần quan trọng nhất)</t>
   </si>
   <si>
-    <t>ưqqdq</t>
+    <t>PROBLEM-SOLVING</t>
+  </si>
+  <si>
+    <t>Algorithms / Research Stage</t>
+  </si>
+  <si>
+    <t>Xây dựng logic gợi ý chi nhánh thay thế khi cơ sở hiện tại full slot.</t>
+  </si>
+  <si>
+    <t>Hãy đề xuất flow cho tính năng suggest alternative branch trong hệ thống spa đa chi nhánh.</t>
+  </si>
+  <si>
+    <t>AI đề xuất kiểm tra slot available theo branch, sau đó suggest các branch gần nhất còn chỗ và cho phép customer chuyển sang branch khác.</t>
+  </si>
+  <si>
+    <t>Tôi bổ sung điều kiện ưu tiên khoảng cách gần khách hàng và thời gian trống gần nhất thay vì chỉ random branch. Tôi quyết định feature này là business logic trọng tâm của project.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -68,6 +83,13 @@
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="163"/>
     </font>
   </fonts>
   <fills count="2">
@@ -105,13 +127,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -370,17 +395,27 @@
       </c>
     </row>
     <row r="2" spans="1:7" ht="86.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
+      <c r="C2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="3" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>

--- a/AI Audit Log_DE190499.xlsx
+++ b/AI Audit Log_DE190499.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FPT Uni\Major5\SWP\ai-audit-log-btuejan11\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B338C2CB-67F3-4725-92F1-107F457D19AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3DB8370-2A36-46CA-B311-8B43D3B6248D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="tạo cho tôi 1 trang tính có đủ " sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet 2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="25">
   <si>
     <t>STT (Entry #)</t>
   </si>
@@ -65,13 +66,60 @@
   </si>
   <si>
     <t>Tôi bổ sung điều kiện ưu tiên khoảng cách gần khách hàng và thời gian trống gần nhất thay vì chỉ random branch. Tôi quyết định feature này là business logic trọng tâm của project.</t>
+  </si>
+  <si>
+    <t>Exploration / Validation (Khám phá &amp; Xác thực)</t>
+  </si>
+  <si>
+    <t>Requirements Engineering (Phân tích yêu cầu - Khởi tạo Use Case)</t>
+  </si>
+  <si>
+    <t>Bạn đã tự lên một danh sách sơ bộ gồm 4 Actor (Owner, Guest, Customer, Staff, Branch Manager) và một số Use Case cơ bản nhưng chưa biết đã đủ số lượng (tối thiểu 25) và đúng nghiệp vụ thực tế/yêu cầu môn SWP chưa.</t>
+  </si>
+  <si>
+    <t>"để xây dựng 1 hệ thống quản lý spa nhiều chi nhánh thì những usecase này đã ổn chưa ? Tôi cần ít nhất 25 usecase để có thể xây dựng dự án này. Bạn xem những đối tượng và những usecase đã hợp lý chưa và cần bổ sung những cái gì để web này đúng nghiệp vụ và có thể đạt yêu cầu trong môn SWP tại đại học fpt..."</t>
+  </si>
+  <si>
+    <t>AI nhận xét bộ khung đạt 70%. Chỉ ra các lỗi phân quyền sai (Staff quản lý dịch vụ/khiếu nại) và thiếu các phân hệ cốt lõi (Liệu trình, Thanh toán, Kho). Đề xuất lại ma trận 28 Use Cases chia làm 5 phân hệ mạch lạc và đưa ra các lưu ý về Multi-branch, xử lý xung đột lịch.</t>
+  </si>
+  <si>
+    <t>Optimization / Deep-dive (Tối ưu &amp; Đào sâu)</t>
+  </si>
+  <si>
+    <t>Requirements Engineering (Hoàn thiện tài liệu SRS / Use Case)</t>
+  </si>
+  <si>
+    <t>Muốn kiểm tra xem danh sách 28 Use Case đã bao phủ 100% nghiệp vụ Spa chuỗi chưa hay vẫn còn rủi ro bị thầy cô bắt bẻ (gap) khi phản biện.</t>
+  </si>
+  <si>
+    <t>AI phân tích các "lỗ hổng" thực tế ngoài đời của Spa: Đặt cọc chống bùng lịch, Điều chuyển kho giữa các chi nhánh, Chia hoa hồng nhân viên, và Thẻ thành viên. Tối ưu và mở rộng hệ thống lên 35 Use Cases hoàn chỉnh. Đưa ra 3 kịch bản phản biện kinh điển của Hội đồng (Luồng gói liệu trình chéo chi nhánh, Tự động trừ vật tư, Isolation dữ liệu).</t>
+  </si>
+  <si>
+    <t>Delta: Nhận ra việc phân quyền ban đầu cho Staff quá rộng và 
+phi thực tế. Phát hiện lỗ hổng lớn về việc thiếu luồng tiền
+ (Hóa đơn/Thanh toán) và quản lý kho.Reflection: Hiểu 
+được tính chất khắt khe của môn SWP tại FPT về mặt phân
+ quyền và tính thực tế. Cần tập trung cô lập dữ liệu theo từng 
+branch_id.</t>
+  </si>
+  <si>
+    <t>Delta: Bổ sung được các Use Case mang tính "sống còn" của mô 
+hình chuỗi (Điều chuyển kho liên chi nhánh, đặt cọc giữ chỗ online).
+ Hệ thống nâng tầm từ quản lý lịch hẹn đơn thuần thành một ERP
+ Spa thu nhỏ.Reflection: Có thêm tư duy phản biện để chuẩn bị 
+cho buổi Defense. Nhận ra tầm quan trọng của việc đồng bộ dữ 
+liệu tập trung trên Cloud để giải bài toán khách đi liệu trình chéo
+ chi nhánh.</t>
+  </si>
+  <si>
+    <t>"sử dụng hết usecase này là nó đã đúng hết tất cả các nghiệp vụ của 1 spa nhiều chi nhánh chưa hay còn thiếu những gì ? Phân tích thật kỹ những Use case trên và nếu thiếu những gì ảnh hưởng đến nghiệp vụ và đặc thù của một spa thì hãy tối ưu giúp tôi nhé"</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -91,6 +139,13 @@
       <family val="2"/>
       <charset val="163"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -100,7 +155,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -123,11 +178,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -136,6 +206,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -591,4 +670,261 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84D5AA1E-FDBE-43E3-88E4-1F1FCD1EE500}">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:I21"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.33203125" customWidth="1"/>
+    <col min="2" max="2" width="24.33203125" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" customWidth="1"/>
+    <col min="4" max="4" width="29.33203125" customWidth="1"/>
+    <col min="5" max="5" width="26.33203125" customWidth="1"/>
+    <col min="6" max="6" width="29.21875" customWidth="1"/>
+    <col min="7" max="7" width="57.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="31.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="205.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+    </row>
+    <row r="3" spans="1:9" ht="196.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
+        <v>2</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+    </row>
+    <row r="4" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+    </row>
+    <row r="5" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+    </row>
+    <row r="6" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+    </row>
+    <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+    </row>
+    <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+    </row>
+    <row r="9" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+    </row>
+    <row r="10" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+    </row>
+    <row r="11" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+    </row>
+    <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+    </row>
+    <row r="13" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+    </row>
+    <row r="14" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+    </row>
+    <row r="15" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+    </row>
+    <row r="16" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+    </row>
+    <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+    </row>
+    <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+    </row>
+    <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+    </row>
+    <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+    </row>
+    <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/AI Audit Log_DE190499.xlsx
+++ b/AI Audit Log_DE190499.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FPT Uni\Major5\SWP\ai-audit-log-btuejan11\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3DB8370-2A36-46CA-B311-8B43D3B6248D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C99433F2-1834-4FC7-993E-158F82B0AABB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/AI Audit Log_DE190499.xlsx
+++ b/AI Audit Log_DE190499.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FPT Uni\Major5\SWP\ai-audit-log-btuejan11\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C99433F2-1834-4FC7-993E-158F82B0AABB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2607CF9-6D7F-4B07-801B-7DAFD9517A52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet 2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="95">
   <si>
     <t>STT (Entry #)</t>
   </si>
@@ -114,16 +115,253 @@
   <si>
     <t>"sử dụng hết usecase này là nó đã đúng hết tất cả các nghiệp vụ của 1 spa nhiều chi nhánh chưa hay còn thiếu những gì ? Phân tích thật kỹ những Use case trên và nếu thiếu những gì ảnh hưởng đến nghiệp vụ và đặc thù của một spa thì hãy tối ưu giúp tôi nhé"</t>
   </si>
+  <si>
+    <t>STT
+(Entry #)</t>
+  </si>
+  <si>
+    <t>Loại Prompt
+(Prompt Type)</t>
+  </si>
+  <si>
+    <t>Giai đoạn
+(Stage/Component)</t>
+  </si>
+  <si>
+    <t>Vấn đề/Ngữ cảnh
+(Problem/Context)</t>
+  </si>
+  <si>
+    <t>Câu lệnh gửi AI
+(Prompt to AI)</t>
+  </si>
+  <si>
+    <t>Tóm tắt phản hồi của AI
+(AI Response Summary)</t>
+  </si>
+  <si>
+    <t>Human Delta &amp; Reflection
+(Phần quan trọng nhất)</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Exploratory
+(Khám phá)</t>
+  </si>
+  <si>
+    <t>Research &amp;
+Branding Direction</t>
+  </si>
+  <si>
+    <t>Claude: "Tôi đang thiết kế UI cho chuỗi spa cao cấp tên AuraSpa tại VN. Đề xuất: (1) bảng màu luxury spa, (2) cặp font serif+sans gợi cảm giác sang trọng &amp; thư giãn, (3) tone of voice copywriting, (4) danh sách màn hình ưu tiên cần thiết kế."</t>
+  </si>
+  <si>
+    <t>Claude đề xuất Burgundy #6B2737 + Cream #F5EDE3, font Playfair Display + Inter, tone 'thanh lịch - tĩnh lặng - chữa lành'. Liệt kê 8 màn hình ưu tiên: Homepage, Login, Customer Dashboard, Booking, Services, Blog, Admin Dashboard, Therapist Schedule.</t>
+  </si>
+  <si>
+    <t>Giữ nguyên palette màu — rất khớp cảm giác spa Việt cao cấp. Tagline 'Đánh thức giác quan, Tìm lại bản ngã' do mình tự viết vì Claude đưa ra tiếng Anh chưa phù hợp thị trường nội địa. Quyết định thiết kế song ngữ Việt-Anh từ đầu.</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Generative
+(Tạo sinh)</t>
+  </si>
+  <si>
+    <t>Homepage &amp;
+Landing Page</t>
+  </si>
+  <si>
+    <t>Thiết kế trang chủ website AuraSpa — cần truyền tải cảm giác sang trọng, tĩnh lặng và thuyết phục khách đặt lịch ngay lần đầu ghé thăm</t>
+  </si>
+  <si>
+    <t>Stitch: Tạo homepage AuraSpa. Hero section ảnh phòng spa + tagline 'Nơi Tĩnh Lặng Gặp Gỡ Sự Sang Trọng'. Sections: triết lý thương hiệu, dịch vụ nổi bật grid ảnh, testimonials 3 cột, CTA đặt lịch nền tối. Màu: burgundy #6B2737, cream #F5EDE3. Font serif heading.</t>
+  </si>
+  <si>
+    <t>Stitch tạo homepage: hero với overlay text trên ảnh phòng trị liệu, section triết lý có ảnh + 3 USP bullet (15+ năm, chuyên gia, không gian riêng), grid dịch vụ 2x2 ảnh đẹp, testimonial cards 3 cột, footer CTA nền tối. Layout clean, đúng brand.</t>
+  </si>
+  <si>
+    <t>Thêm 2 CTA trên hero: 'Đặt Lịch Ngay' + 'Xem Dịch Vụ' — khách lần đầu cần khám phá trước khi quyết định. Số hotline thêm vào hero theo yêu cầu stakeholder. Badge '15+ năm' mình chủ động thêm để tăng trust signal.</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Login &amp; Auth
+Screen</t>
+  </si>
+  <si>
+    <t>Màn hình đăng nhập/đăng ký cho khách — cần vừa chuyên nghiệp vừa giữ cảm xúc thương hiệu, không lạnh lùng như form thông thường</t>
+  </si>
+  <si>
+    <t>Stitch: Tạo màn hình login AuraSpa. Layout 2 cột: trái hero image toàn màn hình với tagline 'Đánh thức giác quan, Tìm lại bản ngã' + 'Since 2024'; phải form tab Đăng nhập/Đăng ký, Email + Mật khẩu, checkbox ghi nhớ, social login Google &amp; Facebook. Màu brand AuraSpa.</t>
+  </si>
+  <si>
+    <t>Stitch tạo split-screen đẹp: bên trái ảnh spa tone vàng-xanh với tagline lớn, bên phải form clean — tab switch Đăng nhập/Đăng ký, input fields minimalist, nút 'Đăng nhập ngay' burgundy, social buttons Google + Facebook outline, footer links đầy đủ.</t>
+  </si>
+  <si>
+    <t>Copy dưới tiêu đề 'Vui lòng nhập thông tin để tiếp tục hành trình thư giãn của bạn' — mình tự viết để maintain cảm xúc brand ngay từ bước auth. Ảnh bên trái thay lại cho đúng không gian thực tế. Social login giữ nguyên vì phù hợp hành vi người dùng Việt Nam.</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Customer Dashboard
+(Sau đăng nhập)</t>
+  </si>
+  <si>
+    <t>Trang chủ sau đăng nhập cho khách hàng — cần cá nhân hóa trải nghiệm, hiển thị điểm loyalty, lịch hẹn sắp tới và gợi ý dịch vụ phù hợp hồ sơ da từng người</t>
+  </si>
+  <si>
+    <t>Stitch: Tạo Customer Home Dashboard AuraSpa (mobile web). Personalized greeting theo tên. Hiển thị: hạng Thành Viên Gold, điểm tích lũy 4.250 (còn 750 đến Platinum), lịch hẹn sắp tới, chi nhánh gần nhất có ảnh+khoảng cách, lịch sử 2 dịch vụ gần đây, section gợi ý 'Dành riêng cho bạn', CTA Đặt lịch ngay.</t>
+  </si>
+  <si>
+    <t>Stitch tạo dashboard cá nhân: greeting 'Chào mừng trở lại, Anh Đào', badge Thành Viên Gold + progress bar điểm, card lịch hẹn Tháng 10/24 'Đã xác nhận', widget chi nhánh AuraSpa Thảo Điền 2.4km, 2 lịch sử dịch vụ gần nhất, card gợi ý Nâng Cơ RF với nút Tìm hiểu ngay.</t>
+  </si>
+  <si>
+    <t>Section 'Dành riêng cho Anh Đào' gợi ý theo lịch sử chăm sóc da — insight mình thêm vào prompt lần 2 vì AI không biết cần personalize theo loại dịch vụ da liễu. Nút 'Chỉ đường &amp; Đặt hẹn' trong widget chi nhánh — insight từ phỏng vấn thực tế khách hay hỏi đường.</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Booking Flow
+(Mobile — Bước 1/4)</t>
+  </si>
+  <si>
+    <t>Luồng đặt lịch mobile 4 bước: chọn dịch vụ → chi nhánh → thời gian → chuyên gia. Cần tối ưu UX, giảm friction tối đa, hiển thị đủ thông tin để quyết định nhanh</t>
+  </si>
+  <si>
+    <t>Stitch: Tạo màn hình Booking mobile AuraSpa bước 1/4. Progress indicator. Service list cards: ảnh nhỏ, tên, thời gian, rating, giá. Section chọn chi nhánh. Date picker horizontal T2-T7. Time slot grid 6 ô. Avatar row chọn chuyên gia. Bottom sticky bar: tổng tiền + thời gian dự kiến + nút XÁC NHẬN. Màu brand.</t>
+  </si>
+  <si>
+    <t>Stitch tạo booking screen: progress bar '1/4 Chọn dịch vụ', 2 service cards (Massage Đá Nóng 1.2tr/90p rating 4.9, Chăm Sóc Da 950k/60p rating 4.8), 2 chi nhánh radio list, date picker ngang T18-T23, 6 time slots grid (10:30 selected), 3 avatar chuyên gia, bottom bar 1.200.000đ + 90 Phút + nút XÁC NHẬN.</t>
+  </si>
+  <si>
+    <t>Gộp chọn chi nhánh vào bước 1 thay vì tách riêng — giảm tổng số bước từ 5 xuống 4. Thêm 'Thời gian dự kiến: 90 Phút' vào bottom bar — khách spa quan tâm duration trước khi confirm. Slot và ngày điều chỉnh khớp giờ hoạt động thực tế 9:00-17:30.</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>Service Menu Page
+(Web)</t>
+  </si>
+  <si>
+    <t>Trang danh mục dịch vụ website — cần đẹp như spa catalog luxury, phân loại rõ theo nhóm, đủ thông tin để khách so sánh và quyết định đặt lịch</t>
+  </si>
+  <si>
+    <t>Stitch: Tạo trang Services AuraSpa. Header: 'Nghệ Thuật Tận Hưởng' + tab filter (Massage/Chăm Sóc Da/Trị Liệu Toàn Thân/Gói Đặc Biệt). Grid dịch vụ theo nhóm: ảnh, tên, mô tả, thời gian, giá. Gói đặc biệt dạng featured card 2 cột to hơn. Tone luxury spa, màu brand.</t>
+  </si>
+  <si>
+    <t>Stitch tạo trang dịch vụ: heading serif italic 'Nghệ Thuật Tận Hưởng', 4 tab filter, grid 4 cột Massage, grid 4 cột Da Mặt, grid 3 cột Trị Liệu Toàn Thân (6 dịch vụ Detox/Khoáng/Men Gạo...), 2 featured cards lớn Gói Hành Trình Wellness. Giá và thời gian hiển thị rõ ràng.</t>
+  </si>
+  <si>
+    <t>Thêm tagline phụ dưới heading từng nhóm — AI không có context thông điệp marketing cụ thể. Grid Trị Liệu Toàn Thân đổi 4→3 cột vì copy dài hơn. Giá thực tế do team spa cung cấp, AI dùng placeholder. Button 'Xem chi tiết' thêm vào từng card sau khi review UX flow.</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>Blog / Wellness
+Journey Page</t>
+  </si>
+  <si>
+    <t>Trang blog content marketing về wellness — AuraSpa muốn xây dựng cộng đồng và SEO, cần giao diện đẹp như tạp chí để tăng thời gian đọc và tỷ lệ subscribe</t>
+  </si>
+  <si>
+    <t>Stitch: Tạo trang Blog AuraSpa. Hero: 'Mẹo Làm Đẹp &amp; Sống Khỏe' + mô tả + search bar. Filter tabs: Tất cả, Chăm sóc da, Thiền định, Dinh dưỡng, Lối sống, Tinh dầu. Grid 3 cột bài viết: ảnh lớn, category badge màu đất, tiêu đề, tóm tắt, ngày + phút đọc. CTA tải thêm. Section newsletter cuối trang.</t>
+  </si>
+  <si>
+    <t>Stitch tạo trang blog dạng magazine: heading lớn, search bar full-width, 6 pill tabs filter, grid 3x2 với 6 bài viết ảnh tone warm (thiền, skincare, thực phẩm, yoga), category badges màu đất, 'Tải thêm bài viết' button, newsletter section 'Gia nhập cộng đồng Aura' + email field + 'Đăng Ký Ngay'.</t>
+  </si>
+  <si>
+    <t>Số phút đọc ('10 phút đọc') thêm vào metadata — insight từ quan sát blog wellness quốc tế. Ảnh thực tế từ thư viện spa thay ảnh placeholder AI. Section newsletter đổi tone thành 'bí quyết làm đẹp độc quyền và ưu đãi sớm nhất' — cụ thể hơn, convert tốt hơn.</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>Admin Dashboard
+(Tổng quan Quản trị)</t>
+  </si>
+  <si>
+    <t>Màn hình tổng quan cho Quản trị viên chi nhánh — cần xem KPI trong ngày, phê duyệt lịch chờ duyệt, theo dõi biểu đồ tăng trưởng doanh thu theo tuần/tháng/năm</t>
+  </si>
+  <si>
+    <t>Stitch: Tạo Admin Dashboard hệ thống AuraSpa. Sidebar: logo, avatar Quản trị viên Chi nhánh Quận 1, menu phân nhóm (Thống kê/Vận hành/Hệ thống). Main: greeting + nút 'Tạo mới tác vụ', 4 KPI cards (Doanh thu ngày, Lịch hẹn hôm nay, Nhân sự trực, Kho hàng) có badge trạng thái, biểu đồ tăng trưởng tuần, right panel Chờ phê duyệt.</t>
+  </si>
+  <si>
+    <t>Stitch tạo admin dashboard: sidebar cố định với đầy đủ menu, 4 KPI cards (+12.5% doanh thu, 8 Mới lịch hẹn, Ổn định nhân sự, 2 Sắp hết kho hàng), line chart tăng trưởng T2-CN, right panel 3 lịch chờ duyệt (Lê Thu Hà/Hoàng Minh/Nguyễn Anh) + nút Duyệt nhanh/Chi tiết.</t>
+  </si>
+  <si>
+    <t>Badge '2 Sắp hết' đỏ cam trên KPI Kho hàng — insight domain-specific: spa cần alert vật tư (dầu, khăn, sản phẩm). Nút '+ Tạo mới tác vụ' mình tự thêm vào header. Toggle Tuần/Tháng/Năm đổi default sang 'Tuần' vì manager thực tế review theo tuần.</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>Therapist Schedule
+(Lịch trình &amp; Phòng)</t>
+  </si>
+  <si>
+    <t>Màn hình làm việc của Kỹ thuật viên Trị liệu — cần xem lịch biểu theo giờ, trạng thái phòng và thông tin khách kế tiếp với cảnh báo bệnh lý/dị ứng quan trọng</t>
+  </si>
+  <si>
+    <t>Stitch: Tạo màn hình Therapist App AuraSpa. Header: tên KTV Minh Anh + 'Đang trực Tầng 2'. Sidebar: Lịch trình, Khách hàng, Kho vật tư, Báo cáo. Timeline 8:00-12:00 với appointment blocks (tên khách, dịch vụ, phòng, trạng thái, nút Hoàn tất/Bắt đầu). Right panel: room grid 4 phòng, customer card khách tiếp theo, lưu ý y tế, tin nhắn lễ tân.</t>
+  </si>
+  <si>
+    <t>Stitch tạo màn hình therapist: badge 'Đang trực Tầng 2' xanh lá, timeline 2 appointment (Chị Nguyễn Lan 9:00 VIP02 Đang chạy; Chị Hoàng Mai 10:30 Chờ phòng), room grid 4 ô (VIP01 Sạch, VIP02 Đang dùng, Deluxe03 Dọn dẹp, Deluxe04 Bảo trì), customer card + lưu ý dị ứng + tin nhắn Lễ tân.</t>
+  </si>
+  <si>
+    <t>Box 'Lưu ý quan trọng: Dị ứng tinh dầu hạt' — insight quan trọng nhất mình chủ động thêm vào prompt lần 2 vì therapist phải thấy thông tin y tế trước khi bắt đầu. AI không tự nghĩ ra warning này. Field 'KTV ưu tiên: Minh Anh, Tuyết' trong customer card — giúp phân công đúng người theo lịch sử.</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Evaluative +
+Generative</t>
+  </si>
+  <si>
+    <t>Strategic Report &amp;
+AI Insights Screen</t>
+  </si>
+  <si>
+    <t>Sau 8 màn hình vận hành, cần thiết kế màn hình báo cáo chiến lược với tính năng AI đề xuất — differentiator của AuraSpa so với phần mềm spa thông thường trên thị trường</t>
+  </si>
+  <si>
+    <t>Claude: "Tôi muốn thêm AI features vào hệ thống AuraSpa. Đề xuất: (1) AI insight nào có giá trị nhất cho owner chuỗi spa? (2) Cách hiển thị AI recommendation trên dashboard chiến lược? (3) Alert/action AI nào nên tự động gợi ý?" Sau đó dùng Stitch render màn hình theo framework Claude đề xuất.</t>
+  </si>
+  <si>
+    <t>Claude đề xuất 3 AI insights: (1) Tối ưu nhân sự giờ cao điểm (dự báo 25% nhu cầu T6 tối), (2) Retargeting VIP chưa quay lại &gt;30 ngày (142 khách, ưu đãi 15%), (3) Xu hướng Detox tăng 40% — mở rộng danh mục. Gợi ý panel 'Chiến lược AI Đề xuất' với badge Quan trọng/Marketing/Xu hướng.</t>
+  </si>
+  <si>
+    <t>Stitch render toàn bộ màn hình Báo cáo Chiến lược: 4 KPI cards (Lợi nhuận ròng 458tr, Chi phí 820tr, 2.450 khách, CSAT 94%), grouped bar chart doanh thu+công suất 6 tháng, bảng tài chính 4 tháng, panel AI 3 cards, widget 3 chi nhánh realtime. Workflow: Claude plan → Stitch render — hiệu quả nhất cho màn hình phức tạp.</t>
+  </si>
+  <si>
+    <t>Cần xác định định hướng thương hiệu và visual identity cho AuraSpa trước khi bắt đầu thiết kế bất kỳ màn hình nào</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -146,16 +384,37 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E79"/>
+        <bgColor rgb="FF1F4E79"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -193,32 +452,59 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFAAAAAA"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFAAAAAA"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFAAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFAAAAAA"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{679B5E49-DA20-4155-934C-81DD4CB35B43}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -927,4 +1213,275 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8095962D-6AA5-44B9-881D-99D43448B400}">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="7" style="9" customWidth="1"/>
+    <col min="2" max="2" width="18" style="9" customWidth="1"/>
+    <col min="3" max="3" width="22" style="9" customWidth="1"/>
+    <col min="4" max="4" width="30" style="9" customWidth="1"/>
+    <col min="5" max="7" width="38" style="9" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>93</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/AI Audit Log_DE190499.xlsx
+++ b/AI Audit Log_DE190499.xlsx
@@ -8,21 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FPT Uni\Major5\SWP\ai-audit-log-btuejan11\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2607CF9-6D7F-4B07-801B-7DAFD9517A52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C588B66-48B6-4E41-9D06-9AD1EBAFA3E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet 2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="4" r:id="rId3"/>
+    <sheet name="Week 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Week 2" sheetId="2" r:id="rId2"/>
+    <sheet name="Week 3" sheetId="5" r:id="rId3"/>
+    <sheet name="Week 4" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="125">
   <si>
     <t>STT (Entry #)</t>
   </si>
@@ -345,16 +346,174 @@
   <si>
     <t>Cần xác định định hướng thương hiệu và visual identity cho AuraSpa trước khi bắt đầu thiết kế bất kỳ màn hình nào</t>
   </si>
+  <si>
+    <t>Mở rộng Chi tiết</t>
+  </si>
+  <si>
+    <t>UC-10: Đặt Lịch Hẹn
+Luồng Chính</t>
+  </si>
+  <si>
+    <t>Luồng tuyến tính thiếu logic xác thực, kiểm tra trạng thái hệ thống. Cần kiểm tra tính khả dụng thực tế, ngăn chặn đặt quá giới hạn (BR-19), cân bằng tải kỹ thuật viên (BR-20), tích hợp discount (UC-14).</t>
+  </si>
+  <si>
+    <t>Mở rộng Luồng Chính 10→16 bước. Mỗi bước: hệ thống kiểm tra gì (tên trường, ràng buộc), tích hợp với UCs/BRs khác, xử lý lỗi. Tập trung phase xác nhận (tính toán giá, xác thực discount, xác nhận).</t>
+  </si>
+  <si>
+    <t>16 bước chi tiết:
+• Bước 5a-5c: Kiểm tra khe trống, booking đồng thời, xác thực chi nhánh
+• Bước 7a-7b: Validate discount API, tính toán lại giá
+• Bước 9-10: Tạo lịch hẹn, kích hoạt UC-38
+✓ Thêm: Kiểm tra trạng thái Đóng cửa tạm thời (BR-46)
+✓ Xử lý race condition với re-validation</t>
+  </si>
+  <si>
+    <t>Phát hiện Exception</t>
+  </si>
+  <si>
+    <t>UC-24: Tạo Hóa đơn
+Mở rộng Exception &amp; BR</t>
+  </si>
+  <si>
+    <t>Chỉ 2 exception; thiếu gói nhiều buổi, hoàn tiền từng phần, tính hoa hồng kỹ thuật viên, VAT (Việt Nam), hủy hóa đơn, tích hợp tồn kho (UC-30).</t>
+  </si>
+  <si>
+    <t>8 exception flow: deduction nhiều buổi, hoàn tiền, tính commission, lỗi thanh toán, thiếu tồn kho, ngăn trùng lập, áp dụng VAT, chuyển quyền thanh toán. Cộng 5 BR mới cho hóa đơn.</t>
+  </si>
+  <si>
+    <t>8 flow (E1-E8):
+• E3: Nhiều buổi → trừ remaining_sessions
+• E5: Thiếu tồn kho → ghi log, cho phép tạo
+• E7: Áp dụng VAT → thêm dòng, tính vào sổ
++ 5 BR: Tính bất biến, Deduction, Commission, Hủy
+✓ Phát hiện: Commission không có trong spec gốc</t>
+  </si>
+  <si>
+    <t>Tinh chỉnh Luồng Thay thế</t>
+  </si>
+  <si>
+    <t>UC-38: Gửi Thông báo
+Kênh &amp; Độ tin cậy</t>
+  </si>
+  <si>
+    <t>Giả định 1 kênh. Thiếu logic đa kênh (email/SMS/push), bản địa hóa ngôn ngữ, kiểm soát tần suất, failover nhà cung cấp, throttling khối lượng, versioning template.</t>
+  </si>
+  <si>
+    <t>7 luồng thay thế: chọn kênh đa (logic ưu tiên), ngôn ngữ, kiểm soát tần suất (max 2 reminder), failover (retry logic), throttling (50/giây), versioning template.</t>
+  </si>
+  <si>
+    <t>7 flow (2.1-2.7):
+• 2.1: Logic chọn kênh + fallback
+• 2.4: Retry failover 5-giây, cảnh báo admin
+• 2.5: Message queue + batch worker (50/sec)
++ 2 BR: Versioning, Throttling
+✓ Thêm: message_queue architecture, failover</t>
+  </si>
+  <si>
+    <t>Làm Rõ Điều kiện Trước</t>
+  </si>
+  <si>
+    <t>UC-27: Cấu hình Khe Thời gian
+Dependencies &amp; Constraints</t>
+  </si>
+  <si>
+    <t>Điều kiện trước mơ hồ: scope access control không rõ, phương thức tạo khe không định nghĩa, dependency schedule thiếu, constraint validation vắng, impact cấu hình trên appointment hiện tại mờ.</t>
+  </si>
+  <si>
+    <t>Chi tiết điều kiện trước: access control (chỉ chi nhánh mình?), dependencies (khe pre-created vs. dynamic), constraint validation (min/max concurrent), impact appointment hiện tại (BR-40), timing postcondition.</t>
+  </si>
+  <si>
+    <t>Điều kiện trước mở rộng:
+• Access: BM chỉ config chi nhánh mình
+• Khe: Cấu trúc pre-created (start, end, duration)
+• Ràng buộc: 1≤concurrent≤active_tech, duration≥min_service
+• Impact: Config từ mai, hôm nay không ảnh hưởng
+✓ Phát hiện: Pre-created vs. dynamic ảnh hưởng kiến trúc</t>
+  </si>
+  <si>
+    <t>Ưu tiên &amp; Tác động</t>
+  </si>
+  <si>
+    <t>UC-29: Giải quyết Khiếu nại
+SLA &amp; Framework Escalation</t>
+  </si>
+  <si>
+    <t>Thiếu taxonomy khiếu nại, mục tiêu SLA, tiêu chí escalation, giới hạn tài chính, liên kết KPI, chiến lược giữ khách, xử lý VIP.</t>
+  </si>
+  <si>
+    <t>8 danh mục khiếu nại → mapping priority + SLA (P1/P2/P3), resolution actions (hoàn tiền/comp limits), escalation rules (khi nào→Owner), tracking financial impact, staff/branch KPI.</t>
+  </si>
+  <si>
+    <t>8 danh mục (Vệ sinh, Billing, Chất lượng, Nhân viên, Cơ sở, Quyền riêng tư, Dị ứng, Feedback) → P1/P2/P3
+SLA: P1&lt;1h ack/24h resolve, P2&lt;8h ack/3d, P3&lt;24h ack/7d
+Escalation: P1, public, comp&gt;300k, VIP, 3+ khiếu nại/6th → Owner
++ 9 BR (BR-62-70)
+✓ Chuyển UC-29 thành KPI driver chiến lược</t>
+  </si>
+  <si>
+    <t>✓ Cải tiến: Luồng giờ đã developer-ready, có tên table, trường cụ thể
+✓ Phát hiện: Thiếu kiểm tra Temporarily Closed (BR-46) → Thêm
+✓ Điều chỉnh: Bước 6 gốc (2 concern) → Tách thành atomic steps
+⚠ Quyết định: Concurrent booking check TRƯỚC hiển thị (pessimistic) hay chỉ lúc confirm (optimistic)?
+  → CHỌN: Optimistic locking step 5c + re-validate step 8 để catch race condition
+✓ THÊM: Explicit error handling path cho mỗi validation failure
+PHẢN LOẠI: UC-10 là transaction-critical, cần detailed validation logic</t>
+  </si>
+  <si>
+    <t>✓ PHÁT HIỆN LỚN: UC-24 không đầy đủ – thiếu multi-session &amp; commission tracking
+✓ THÊM: E3 (Multi-session), E5 (Inventory shortage), E7 (VAT) – quan trọng cho spa VN
+✓ LIÊN KẾT TẠO: UC-24 giờ explicit connect tới UC-30 (Inventory) &amp; staff payroll concerns
+⚠ QUYẾT ĐỊNH: Technician commission là system-wide concern → có thể cần UC-39 "Calculate Staff Commission &amp; Payroll"
+✓ COMPLIANCE: BR-57-BR-61 cover Vietnam tax &amp; spa industry invoice requirements
+PHẢN LOẠI: Original UC-24 quá đơn giản; mở rộng này hỗ trợ real spa business operations</t>
+  </si>
+  <si>
+    <t>✓ CRITICAL ADDITION: Alt Flow 2.4 &amp; 2.5 address production-grade reliability (failover, throttling)
+✓ PHÁT HIỆN: Original UC-38 assume single channel; reality cần multi-channel logic + fallback
+✓ CONCERN MỚI: Notification template versioning là requirement chưa capture
+⚠ ARCHITECTURE IMPACT: Cần design message_queue table &amp; background worker service
+✓ COMPLIANCE: BR-54 (SMS opt-out) giờ integrate vào full channel selection logic
+PHẢN LOẠI: UC-38 tăng từ 3 thành 8+ flows; complex hơn initial spec
+NEXT STEP: Có thể cần UC-39 "Manage Notification Preferences &amp; Templates" (Owner/Manager config)</t>
+  </si>
+  <si>
+    <t>✓ CLARITY: Preconditions giờ explicit define access control, data dependencies, timeline
+✓ PHÁT HIỆN: Assumption slots pre-created (không dynamically generated) – important cho design
+✓ CONSTRAINT ADDED: max_concurrent_bookings không thể exceed active technician count – prevent overbooking
+⚠ COMPLEXITY: Slot structure (pre-created vs. dynamic) affect entire booking system architecture
+✓ TIMING CLARIFICATION: Config changes apply từ next day, không immediately – prevent race conditions
+PHẢN LOẠI: UC-27 actually configuration management UC với significant dependencies trên UC-21, UC-26, real-time slot availability
+NEXT STEP: Create data model cho booking_slot_config &amp; time_slot tables</t>
+  </si>
+  <si>
+    <t>✓ MAJOR EXPANSION: UC-29 tăng từ simple complaint resolution → comprehensive customer service &amp; retention strategy
+✓ CATEGORIES DEFINED: 8 categories with severity/priority mapping → consistent handling across branches
+✓ FINANCIAL CONTROLS: Compensation limits (BR-64) prevent BM over-committing refunds; Owner maintain financial control
+✓ KPI INTEGRATION: Complaints giờ tied to staff performance (retraining triggers), branch ratings (Owner visibility), customer retention
+✓ ESCALATION LOGIC: Clear rules prevent trivial complaints reaching Owner while ensuring critical ones do
+✓ DATA QUALITY: Immutable audit trail (BR-70) support regulatory compliance &amp; dispute resolution
+⚠ NEW CONCERN: Follow-up satisfaction survey (UC-38 extension) tạo feedback loop; need new survey UC or extend UC-38
+⚠ WORKFLOW ADDED: "Risky Customer" detection &amp; VIP prioritization add complexity
+PHẢN LOẠI: UC-29 giờ strategic KPI driver, không chỉ reactive issue handler. Impact Owner dashboards, staff metrics, customer retention
+NEXT STEP: Design complaint dashboard cho Owner showing trends, escalations, staff performance; integrate with UC-31</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -398,6 +557,12 @@
     <font>
       <sz val="9"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="major"/>
     </font>
   </fonts>
   <fills count="3">
@@ -468,43 +633,48 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{679B5E49-DA20-4155-934C-81DD4CB35B43}"/>
+    <cellStyle name="Normal 3" xfId="2" xr:uid="{31554C69-3A9C-4497-AEBA-DA8560C4FB23}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1216,6 +1386,277 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94319FF9-09DD-4364-854F-EE2EC40DD129}">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="7" style="9" customWidth="1"/>
+    <col min="2" max="2" width="18" style="9" customWidth="1"/>
+    <col min="3" max="3" width="22" style="9" customWidth="1"/>
+    <col min="4" max="4" width="30" style="9" customWidth="1"/>
+    <col min="5" max="7" width="38" style="9" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>93</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8095962D-6AA5-44B9-881D-99D43448B400}">
   <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
@@ -1252,234 +1693,164 @@
       </c>
     </row>
     <row r="2" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="F2" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="G2" s="11" t="s">
-        <v>37</v>
+      <c r="B2" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>44</v>
+      <c r="B3" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="B4" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>50</v>
+      <c r="B4" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="G5" s="11" t="s">
-        <v>56</v>
+      <c r="B5" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="B6" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>62</v>
+      <c r="B6" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>68</v>
-      </c>
+      <c r="A7" s="10"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
     </row>
     <row r="8" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>74</v>
-      </c>
+      <c r="A8" s="10"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
     </row>
     <row r="9" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>80</v>
-      </c>
+      <c r="A9" s="10"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
     </row>
     <row r="10" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>86</v>
-      </c>
+      <c r="A10" s="10"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
     </row>
     <row r="11" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>93</v>
-      </c>
+      <c r="A11" s="10"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/AI Audit Log_DE190499.xlsx
+++ b/AI Audit Log_DE190499.xlsx
@@ -8,22 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FPT Uni\Major5\SWP\ai-audit-log-btuejan11\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C588B66-48B6-4E41-9D06-9AD1EBAFA3E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3D87258-E609-49D0-9E19-AD192A5223DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
     <sheet name="Week 2" sheetId="2" r:id="rId2"/>
     <sheet name="Week 3" sheetId="5" r:id="rId3"/>
     <sheet name="Week 4" sheetId="4" r:id="rId4"/>
+    <sheet name="Week 5" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="143">
   <si>
     <t>STT (Entry #)</t>
   </si>
@@ -497,12 +498,66 @@
 PHẢN LOẠI: UC-29 giờ strategic KPI driver, không chỉ reactive issue handler. Impact Owner dashboards, staff metrics, customer retention
 NEXT STEP: Design complaint dashboard cho Owner showing trends, escalations, staff performance; integrate with UC-31</t>
   </si>
+  <si>
+    <t>UI/UX Generation</t>
+  </si>
+  <si>
+    <t>Frontend / Owner Dashboard</t>
+  </si>
+  <si>
+    <t>Cần xây dựng giao diện tổng quan (Dashboard) cho Owner để xem thống kê doanh thu toàn chuỗi spa và số liệu tổng quát.</t>
+  </si>
+  <si>
+    <t>"Viết code HTML/Tailwind CSS cho Dashboard của Owner quản lý chuỗi spa. Yêu cầu có 4 thẻ thống kê (tổng khách, doanh thu, số nhân viên, số chi nhánh) và layout cho biểu đồ doanh thu."</t>
+  </si>
+  <si>
+    <t>AI cung cấp bộ khung HTML chuẩn với layout Grid/Flexbox của Tailwind. Tích hợp sẵn các thẻ card với icon và tạo vùng placeholder cho biểu đồ (Chart.js/Recharts).</t>
+  </si>
+  <si>
+    <t>Đã tinh chỉnh lại màu sắc theo brand guideline của spa. Code layout AI cho khá chuẩn nhưng cần tách các thẻ card ra thành các component nhỏ để tái sử dụng.</t>
+  </si>
+  <si>
+    <t>Refactoring &amp; Responsive</t>
+  </si>
+  <si>
+    <t>Frontend / Branch Manager View</t>
+  </si>
+  <si>
+    <t>Bảng quản lý danh sách nhân viên của Quản lý chi nhánh (Branch Manager) bị vỡ layout trên mobile và thiếu tính năng lọc.</t>
+  </si>
+  <si>
+    <t>"Tối ưu lại đoạn code bảng danh sách nhân viên này bằng Tailwind CSS để responsive trên màn hình nhỏ. Thêm giao diện cho thanh tìm kiếm và bộ lọc theo ca làm việc (Sáng/Chiều)."</t>
+  </si>
+  <si>
+    <t>AI bổ sung overflow-x-auto cho bảng để cuộn ngang trên mobile, đồng thời thêm cấu trúc UI cho Search bar và Dropdown filter ở phía trên bảng.</t>
+  </si>
+  <si>
+    <t>Áp dụng giải pháp responsive thành công. Tự code thêm logic debounce cho ô search và map dữ liệu thật vào. Rút kinh nghiệm: Cần chỉ định rõ breakpoint (sm, md, lg) khi nhờ AI làm responsive.</t>
+  </si>
+  <si>
+    <t>Component Creation</t>
+  </si>
+  <si>
+    <t>Frontend / Staff Manager</t>
+  </si>
+  <si>
+    <t>Cần một giao diện lịch làm việc trong ngày (Daily Schedule) trực quan để nhân viên (Staff/Therapist) xem các lịch hẹn với khách hàng.</t>
+  </si>
+  <si>
+    <t>"Tạo một component giao diện lịch làm việc trong ngày cho nhân viên spa (từ 8h sáng - 20h tối). Các slot có lịch hẹn cần hiển thị thẻ thông tin khách và có màu khác nhau theo trạng thái (chờ, đang làm, hoàn thành)."</t>
+  </si>
+  <si>
+    <t>AI thiết kế một giao diện dạng timeline dọc. Sử dụng CSS class để phân loại màu sắc trạng thái (vàng cho chờ, xanh cho hoàn thành) và chia các khoảng thời gian theo từng giờ.</t>
+  </si>
+  <si>
+    <t>Đã chia nhỏ lại các slot thời gian thành 30 phút/slot thay vì 1 giờ cho khớp với thời lượng liệu trình thực tế của spa. Ý tưởng timeline của AI rất trực quan và dễ sử dụng.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -564,8 +619,13 @@
       <family val="2"/>
       <scheme val="major"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF434343"/>
+      <name val="Roboto"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -578,8 +638,20 @@
         <bgColor rgb="FF1F4E79"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F8F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -632,13 +704,148 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF284E3F"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF284E3F"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF6F8F9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF284E3F"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF6F8F9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF284E3F"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF284E3F"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF6F8F9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF284E3F"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFF6F8F9"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF6F8F9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFF6F8F9"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF6F8F9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF284E3F"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF6F8F9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF284E3F"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF284E3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF284E3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF284E3F"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF284E3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -669,6 +876,33 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1855,4 +2089,177 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A77F9E7-3ECA-4247-809A-49DA9747BEA3}">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="7" style="9" customWidth="1"/>
+    <col min="2" max="2" width="18" style="9" customWidth="1"/>
+    <col min="3" max="3" width="22" style="9" customWidth="1"/>
+    <col min="4" max="4" width="30" style="9" customWidth="1"/>
+    <col min="5" max="7" width="38" style="9" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="120" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="13">
+        <v>1</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="G2" s="15" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="120" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="16">
+        <v>2</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="G3" s="18" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="120" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="19">
+        <v>3</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="12"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+    </row>
+    <row r="6" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="12"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+    </row>
+    <row r="7" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="10"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+    </row>
+    <row r="8" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="10"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+    </row>
+    <row r="9" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="10"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+    </row>
+    <row r="10" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="10"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+    </row>
+    <row r="11" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="10"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/AI Audit Log_DE190499.xlsx
+++ b/AI Audit Log_DE190499.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FPT Uni\Major5\SWP\ai-audit-log-btuejan11\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3D87258-E609-49D0-9E19-AD192A5223DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC562C12-EDE0-4A3B-A895-C3845E6D3953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
@@ -18,13 +18,14 @@
     <sheet name="Week 3" sheetId="5" r:id="rId3"/>
     <sheet name="Week 4" sheetId="4" r:id="rId4"/>
     <sheet name="Week 5" sheetId="6" r:id="rId5"/>
+    <sheet name="Week 6" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="169">
   <si>
     <t>STT (Entry #)</t>
   </si>
@@ -551,6 +552,84 @@
   </si>
   <si>
     <t>Đã chia nhỏ lại các slot thời gian thành 30 phút/slot thay vì 1 giờ cho khớp với thời lượng liệu trình thực tế của spa. Ý tưởng timeline của AI rất trực quan và dễ sử dụng.</t>
+  </si>
+  <si>
+    <t>API Integration</t>
+  </si>
+  <si>
+    <t>Frontend / Auth Flow</t>
+  </si>
+  <si>
+    <t>Cần tích hợp API đăng nhập và phân quyền cho 3 vai trò: Owner, Branch Manager và Staff/Therapist. Mỗi vai trò cần redirect đến Dashboard khác nhau sau khi login thành công.</t>
+  </si>
+  <si>
+    <t>"Viết code React cho màn hình Login có form email/password, gọi API POST /auth/login, xử lý JWT token trả về và redirect theo role (owner → /owner/dashboard, manager → /manager/dashboard, staff → /staff/schedule). Dùng React Router v6 và axios."</t>
+  </si>
+  <si>
+    <t>AI tạo LoginPage component với form validation cơ bản, axios interceptor để lưu token vào localStorage, hàm decodeJWT để đọc role, và useNavigate để redirect. Cũng gợi ý thêm PrivateRoute wrapper.</t>
+  </si>
+  <si>
+    <t>Bổ sung thêm xử lý refresh token và logout tự động khi token hết hạn — AI không đề xuất sẵn. Cần tách riêng authContext để quản lý state toàn cục thay vì lưu trực tiếp trong component.</t>
+  </si>
+  <si>
+    <t>Cần thêm biểu đồ doanh thu theo tuần/tháng/năm cho trang Dashboard của Owner. Biểu đồ phải có thể chuyển đổi khoảng thời gian và hiển thị so sánh với kỳ trước.</t>
+  </si>
+  <si>
+    <t>"Tạo component RevenueChart dùng Recharts, nhận props data (array), period (week/month/year) và hiển thị LineChart hoặc BarChart. Có nút toggle để chuyển đổi loại biểu đồ. Thêm đường so sánh với kỳ trước bằng màu khác."</t>
+  </si>
+  <si>
+    <t>AI tạo component với ResponsiveContainer, hai dataset (kỳ hiện tại và kỳ trước) bằng màu khác nhau, nút toggle chart type, tooltip hiển thị cả hai giá trị, và legend rõ ràng.</t>
+  </si>
+  <si>
+    <t>Tự bổ sung loading skeleton khi fetch data và empty state khi không có dữ liệu — AI bỏ qua. Format số tiền trong tooltip theo định dạng VND (triệu đồng). Ý tưởng so sánh kỳ trước của AI rất hữu ích.</t>
+  </si>
+  <si>
+    <t>Frontend / Staff Schedule</t>
+  </si>
+  <si>
+    <t>Component lịch làm việc theo ngày (Daily Schedule từ tuần trước) cần mở rộng thành lịch theo tuần để Staff xem tổng quan 7 ngày. Layout cũ chỉ hiển thị 1 ngày, cần redesign.</t>
+  </si>
+  <si>
+    <t>"Refactor WeeklySchedule component từ daily sang weekly view. Hiển thị grid 7 cột (Thứ 2 → CN), mỗi cột có các appointment slot. Click vào ngày để xem chi tiết. Dùng Tailwind CSS, responsive: mobile scroll ngang, desktop full grid."</t>
+  </si>
+  <si>
+    <t>AI tạo grid 7 cột với overflow-x-scroll trên mobile, mỗi slot hiển thị tên khách và dịch vụ, highlight ngày hiện tại bằng màu nổi bật, click handler truyền selectedDate lên parent.</t>
+  </si>
+  <si>
+    <t>Thêm logic highlight các ngày có lịch dày đặc (&gt;5 appointments) bằng màu cảnh báo — AI không nghĩ đến. Cần fix lỗi timezone khi convert date string từ API sang local time. Mobile UX tốt hơn nhờ gợi ý scroll ngang.</t>
+  </si>
+  <si>
+    <t>Frontend / Branch Manager</t>
+  </si>
+  <si>
+    <t>Cần màn hình báo cáo doanh thu theo chi nhánh cho Branch Manager: xem doanh thu ngày/tuần, danh sách top dịch vụ bán chạy, và tỉ lệ hoàn thành lịch hẹn.</t>
+  </si>
+  <si>
+    <t>"Tạo trang BranchReport với 3 section: (1) Revenue summary card với số liệu hôm nay vs hôm qua, (2) Top 5 services table với số lượt và doanh thu, (3) Appointment completion rate dạng progress bar. Dùng Tailwind, layout responsive 2 cột trên desktop."</t>
+  </si>
+  <si>
+    <t>AI tạo layout 2 cột sạch, các card với shadow và border-radius, bảng top services có sort, progress bar với màu theo mức độ (xanh/vàng/đỏ) và hiển thị phần trăm số liệu.</t>
+  </si>
+  <si>
+    <t>Thêm filter theo khoảng ngày tùy chỉnh thay vì chỉ hôm nay/hôm qua — AI chỉ làm cố định. Export báo cáo ra CSV cũng cần bổ sung thêm. Layout tổng thể AI tạo ra khá chuẩn, tiết kiệm nhiều thời gian.</t>
+  </si>
+  <si>
+    <t>Debugging &amp; Fix</t>
+  </si>
+  <si>
+    <t>Frontend / Booking Flow</t>
+  </si>
+  <si>
+    <t>Màn hình đặt lịch của khách hàng bị lỗi: khi chọn slot thời gian thì state không cập nhật đúng, dẫn đến slot đã chọn không được highlight và submit form gửi sai giờ.</t>
+  </si>
+  <si>
+    <t>"Debug đoạn code React này — khi click chọn slot time, state selectedSlot không re-render đúng. Đây là component BookingCalendar với useState cho selectedSlot và danh sách slots render từ array. [paste code]"</t>
+  </si>
+  <si>
+    <t>AI phát hiện lỗi: object reference trong useState không trigger re-render vì mutate trực tiếp. Đề xuất dùng spread operator hoặc primitive value (slot id string) thay vì object. Giải thích rõ về React shallow comparison.</t>
+  </si>
+  <si>
+    <t>Lỗi đúng như AI chẩn đoán — fix bằng cách lưu selectedSlotId (string) thay vì object. Rút kinh nghiệm quan trọng: luôn dùng primitive value cho selected state trong list. AI giải thích cơ chế re-render rất rõ, giúp hiểu sâu hơn.</t>
   </si>
 </sst>
 </file>
@@ -625,7 +704,7 @@
       <name val="Roboto"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -650,8 +729,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F8FB"/>
+        <bgColor rgb="FFF5F8FB"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -839,13 +924,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -903,6 +1003,18 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2262,4 +2374,205 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{042921DE-EE13-4C42-A1E5-8CBEDAB43FCA}">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="7" style="9" customWidth="1"/>
+    <col min="2" max="2" width="18" style="9" customWidth="1"/>
+    <col min="3" max="3" width="22" style="9" customWidth="1"/>
+    <col min="4" max="4" width="30" style="9" customWidth="1"/>
+    <col min="5" max="7" width="38" style="9" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="120" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="13"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="15"/>
+    </row>
+    <row r="3" spans="1:7" ht="120" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="16"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="18"/>
+    </row>
+    <row r="4" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="22">
+        <v>1</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>143</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="D4" s="23" t="s">
+        <v>145</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="F4" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="G4" s="23" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="24">
+        <v>2</v>
+      </c>
+      <c r="B5" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="D5" s="25" t="s">
+        <v>149</v>
+      </c>
+      <c r="E5" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="F5" s="25" t="s">
+        <v>151</v>
+      </c>
+      <c r="G5" s="25" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="22">
+        <v>3</v>
+      </c>
+      <c r="B6" s="23" t="s">
+        <v>131</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="D6" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="E6" s="23" t="s">
+        <v>155</v>
+      </c>
+      <c r="F6" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="G6" s="23" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="24">
+        <v>4</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>125</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>158</v>
+      </c>
+      <c r="D7" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="E7" s="25" t="s">
+        <v>160</v>
+      </c>
+      <c r="F7" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="G7" s="25" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="22">
+        <v>5</v>
+      </c>
+      <c r="B8" s="23" t="s">
+        <v>163</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>164</v>
+      </c>
+      <c r="D8" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="E8" s="23" t="s">
+        <v>166</v>
+      </c>
+      <c r="F8" s="23" t="s">
+        <v>167</v>
+      </c>
+      <c r="G8" s="23" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="10"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+    </row>
+    <row r="10" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="10"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+    </row>
+    <row r="11" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="10"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/AI Audit Log_DE190499.xlsx
+++ b/AI Audit Log_DE190499.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FPT Uni\Major5\SWP\ai-audit-log-btuejan11\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC562C12-EDE0-4A3B-A895-C3845E6D3953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1FC65F9-AB91-49F7-82F5-23AA8CE3A880}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
@@ -19,13 +19,14 @@
     <sheet name="Week 4" sheetId="4" r:id="rId4"/>
     <sheet name="Week 5" sheetId="6" r:id="rId5"/>
     <sheet name="Week 6" sheetId="7" r:id="rId6"/>
+    <sheet name="Week 7" sheetId="8" r:id="rId7"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="191">
   <si>
     <t>STT (Entry #)</t>
   </si>
@@ -631,16 +632,89 @@
   <si>
     <t>Lỗi đúng như AI chẩn đoán — fix bằng cách lưu selectedSlotId (string) thay vì object. Rút kinh nghiệm quan trọng: luôn dùng primitive value cho selected state trong list. AI giải thích cơ chế re-render rất rõ, giúp hiểu sâu hơn.</t>
   </si>
+  <si>
+    <t>Fix đúng hoàn toàn sau khi áp dụng. Ghi nhớ quan trọng: file CSV export cho người dùng Việt luôn cần BOM UTF-8. AI giải thích kỹ nguyên nhân giúp hiểu sâu, không chỉ copy-paste fix mù quáng.</t>
+  </si>
+  <si>
+    <t>AI chẩn đoán thiếu BOM (Byte Order Mark) UTF-8 ở đầu file khiến Excel đọc sai encoding. Fix bằng cách thêm \uFEFF vào đầu string. Đồng thời format số tiền bằng toLocaleString('vi-VN'). Giải thích rõ vì sao cần BOM.</t>
+  </si>
+  <si>
+    <t>"Fix lỗi export CSV trên BranchReport: tiếng Việt bị lỗi encoding khi download, số tiền không format đúng (cần dạng 1.500.000 thay vì 1500000). Đây là hàm exportToCSV hiện tại dùng Blob và URL.createObjectURL. [paste code]"</t>
+  </si>
+  <si>
+    <t>Trang BranchReport (tạo ở tuần 2) bị lỗi khi export CSV: file tải về bị encoding sai với tiếng Việt (dấu bị mã hoá thành ký tự lạ), và cột số tiền không có định dạng đúng.</t>
+  </si>
+  <si>
+    <t>Thêm prefetch data cho tab kế tiếp khi hover vào tab button — AI không đề xuất. Trang load nhanh hơn rõ rệt sau khi áp dụng. Cần đọc thêm về React Query để hiểu hết các option, AI chỉ dùng basic features.</t>
+  </si>
+  <si>
+    <t>AI refactor sang React Query với queryKey theo tab, Suspense boundary cho mỗi chart, skeleton loading placeholder, và invalidateQueries khi có thao tác cập nhật. Giải thích rõ staleTime vs cacheTime.</t>
+  </si>
+  <si>
+    <t>"Tối ưu performance cho OwnerDashboard: dùng React.lazy + Suspense cho các chart component, implement React Query để cache API calls với staleTime 5 phút, và chỉ fetch data của tab đang active. Giữ nguyên UI hiện tại."</t>
+  </si>
+  <si>
+    <t>Trang Dashboard Owner đang load chậm vì fetch tất cả dữ liệu cùng lúc khi mount. Cần tối ưu lại: lazy load từng section, cache kết quả API và tránh re-fetch không cần thiết khi chuyển tab.</t>
+  </si>
+  <si>
+    <t>Thêm âm thanh thông báo khi có event mới — AI không gợi ý. Cần handle reconnect tự động khi mất mạng, AI có đề cập nhưng chưa implement đầy đủ. Pattern custom hook useSocket rất tái sử dụng được, áp dụng cho nhiều feature khác.</t>
+  </si>
+  <si>
+    <t>AI cung cấp hook useSocket custom để quản lý kết nối, listener cho các event (new_booking, cancel_booking, checkin), NotificationBell với dropdown animate, và lưu notifications vào Context để dùng toàn app.</t>
+  </si>
+  <si>
+    <t>"Tích hợp WebSocket (socket.io-client) vào React app để nhận realtime notification. Tạo NotificationBell component hiển thị icon chuông với badge số chưa đọc, dropdown danh sách thông báo. Connect socket khi login, disconnect khi logout."</t>
+  </si>
+  <si>
+    <t>Cần tích hợp hệ thống thông báo realtime: khi có lịch hẹn mới, hủy lịch hoặc khách check-in, Staff và Manager nhận thông báo ngay trên giao diện mà không cần reload trang.</t>
+  </si>
+  <si>
+    <t>Frontend / Notification</t>
+  </si>
+  <si>
+    <t>Mask số điện thoại (hiện 4 số cuối) cho Staff thường — AI không tự làm. Thêm badge hạng thành viên (Bạc/Vàng/Kim cương) theo số lần ghé. Cách AI xử lý phân quyền hiển thị bằng role từ JWT rất gọn, học được pattern này.</t>
+  </si>
+  <si>
+    <t>AI tạo layout với avatar lớn ở trên, các thẻ thông tin tổng quan, hệ thống tab chuyển đổi mượt, bảng service history có phân trang, và conditional rendering cho tab ghi chú theo role từ JWT.</t>
+  </si>
+  <si>
+    <t>"Tạo trang CustomerProfile cho Staff xem thông tin khách: avatar, tên, SĐT, tổng số lần ghé, điểm thành viên. Tab lịch sử dịch vụ (service history table) và tab ghi chú sức khoẻ (chỉ hiện nếu role là therapist hoặc manager). Dùng Tailwind."</t>
+  </si>
+  <si>
+    <t>Cần trang hồ sơ khách hàng cho phía Staff xem khi nhận lịch: lịch sử dịch vụ đã dùng, ghi chú sức khoẻ/dị ứng, và số lần ghé thăm. Dữ liệu nhạy cảm nên cần phân quyền hiển thị.</t>
+  </si>
+  <si>
+    <t>Frontend / Customer Profile</t>
+  </si>
+  <si>
+    <t>Thêm xử lý lỗi khi API trả về slot đã bị đặt bởi người khác (race condition) — AI không đề cập. Cần hiển thị toast error và cho phép chọn lại slot. Animation checkmark của AI rất ổn, giữ nguyên.</t>
+  </si>
+  <si>
+    <t>AI tạo layout 2 bước: màn hình review dạng card summary và màn hình success với animation checkmark, mã booking được highlight, có nút thêm vào lịch hoặc về trang chủ. Xử lý loading state khi gọi API.</t>
+  </si>
+  <si>
+    <t>"Tạo component BookingConfirmation hiển thị review thông tin đặt lịch: tên dịch vụ, therapist, ngày giờ, giá tiền. Có nút Xác nhận và Quay lại. Sau khi xác nhận, gọi API POST /bookings và hiển thị màn hình thành công với booking code."</t>
+  </si>
+  <si>
+    <t>Sau khi fix lỗi state slot tuần trước, cần hoàn thiện luồng đặt lịch: thêm bước xác nhận trước khi submit (review màn hình), hiển thị thông tin dịch vụ, therapist và giờ đã chọn trước khi thanh toán.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -704,7 +778,7 @@
       <name val="Roboto"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -733,6 +807,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFF5F8FB"/>
         <bgColor rgb="FFF5F8FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B3A5C"/>
+        <bgColor rgb="FF1B3A5C"/>
       </patternFill>
     </fill>
   </fills>
@@ -940,87 +1020,105 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{679B5E49-DA20-4155-934C-81DD4CB35B43}"/>
     <cellStyle name="Normal 3" xfId="2" xr:uid="{31554C69-3A9C-4497-AEBA-DA8560C4FB23}"/>
+    <cellStyle name="Normal 4" xfId="3" xr:uid="{95D042E2-5B87-469A-B2EE-2FC366D5D55A}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2575,4 +2673,160 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB95F3E8-5FE9-4925-B5E5-F56859B18501}">
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6" style="26" customWidth="1"/>
+    <col min="2" max="2" width="18" style="26" customWidth="1"/>
+    <col min="3" max="3" width="22" style="26" customWidth="1"/>
+    <col min="4" max="4" width="35" style="26" customWidth="1"/>
+    <col min="5" max="7" width="45" style="26" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="26"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1" s="31" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="109.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="28">
+        <v>1</v>
+      </c>
+      <c r="B2" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>164</v>
+      </c>
+      <c r="D2" s="27" t="s">
+        <v>190</v>
+      </c>
+      <c r="E2" s="27" t="s">
+        <v>189</v>
+      </c>
+      <c r="F2" s="27" t="s">
+        <v>188</v>
+      </c>
+      <c r="G2" s="27" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="109.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="30">
+        <v>2</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>125</v>
+      </c>
+      <c r="C3" s="29" t="s">
+        <v>186</v>
+      </c>
+      <c r="D3" s="29" t="s">
+        <v>185</v>
+      </c>
+      <c r="E3" s="29" t="s">
+        <v>184</v>
+      </c>
+      <c r="F3" s="29" t="s">
+        <v>183</v>
+      </c>
+      <c r="G3" s="29" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="109.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="28">
+        <v>3</v>
+      </c>
+      <c r="B4" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="C4" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="D4" s="27" t="s">
+        <v>180</v>
+      </c>
+      <c r="E4" s="27" t="s">
+        <v>179</v>
+      </c>
+      <c r="F4" s="27" t="s">
+        <v>178</v>
+      </c>
+      <c r="G4" s="27" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="109.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="30">
+        <v>4</v>
+      </c>
+      <c r="B5" s="29" t="s">
+        <v>131</v>
+      </c>
+      <c r="C5" s="29" t="s">
+        <v>126</v>
+      </c>
+      <c r="D5" s="29" t="s">
+        <v>176</v>
+      </c>
+      <c r="E5" s="29" t="s">
+        <v>175</v>
+      </c>
+      <c r="F5" s="29" t="s">
+        <v>174</v>
+      </c>
+      <c r="G5" s="29" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="109.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="28">
+        <v>5</v>
+      </c>
+      <c r="B6" s="27" t="s">
+        <v>163</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>158</v>
+      </c>
+      <c r="D6" s="27" t="s">
+        <v>172</v>
+      </c>
+      <c r="E6" s="27" t="s">
+        <v>171</v>
+      </c>
+      <c r="F6" s="27" t="s">
+        <v>170</v>
+      </c>
+      <c r="G6" s="27" t="s">
+        <v>169</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>